--- a/output/evidence/第10期計画_エビデンス_2_事業所と公表情報.xlsx
+++ b/output/evidence/第10期計画_エビデンス_2_事業所と公表情報.xlsx
@@ -922,12 +922,12 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>3町の回答4,798票（回収率67.4％）の集計値</t>
+          <t>3町の回答4,798票（回収率67.4％）。うち個票4,729票を令和8年8月に受領しクロス集計・分析に用いた。個人情報のため本集には収録せず、成果品「調査クロス集計・分析」に集計結果を収めている</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>―</t>
         </is>
       </c>
     </row>

--- a/output/evidence/第10期計画_エビデンス_2_事業所と公表情報.xlsx
+++ b/output/evidence/第10期計画_エビデンス_2_事業所と公表情報.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -565,12 +565,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>令和8年7月22日・7月29日・7月30日取得</t>
+          <t>令和8年7月22日・7月29日・7月30日取得、令和8年8月31日受領</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>A系列（人口）・B系列（認定）・C1（保険料）・D系列（受給）・K系列（事業所数）・M系列（従事者数）・W144（交付金評価指標）・δ（介護サービス自給率）</t>
+          <t>A系列（人口）・B系列（認定）・C1（保険料）・D系列（受給）・K系列（事業所数）・M系列（従事者数）・W144（交付金評価指標）・δ（介護サービス自給率）。令和8年8月31日に総括表（6シート）及び管理指標グラフ（7指標）を受領し、第7期から第9期までの計画値・実績値・対計画比を追加した</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>各年3月末現在</t>
+          <t>各年3月末現在。年報（令和6・7年度）及び月報（令和8年4〜7月）は令和8年8月28日受領</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>要介護認定者数・受給者数</t>
+          <t>要介護認定者数・受給者数。年報により給付費・保険料収納率・所得段階別被保険者数・介護給付費準備基金の残高を確定した</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -931,16 +931,112 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="n"/>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-    </row>
-    <row r="18" ht="39" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>⑬</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>厚生労働省</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>令和6年度実績・令和8年8月28日受領</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>市町村Ⅰ〜Ⅲの3表。通いの場の展開状況（箇所数・参加者実人数・運営主体・開催頻度）、一般介護予防事業、サービス・活動事業。構成3町ごとの回答</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>⑭</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>介護保険特別会計歳入歳出決算書</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>大雪地区広域連合</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>令和6年度・令和8年8月28日受領</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>款項別の決算額、実質収支額、介護給付費準備基金の推移。介護保険事業状況報告年報の様式4と22項目すべて一致する</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>⑮</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>介護保険事業財政調整基金条例・介護保険料の減額賦課に伴う処遇改善臨時特例基金条例</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>大雪地区広域連合</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>令和8年8月28日受領</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>基金の設置・積立て・処分の要件。第5条第3項の積立ての上限（計画期間の保険料収納必要額の100分の10）</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+    </row>
+    <row r="21" ht="39" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>注1）「収録先」は本エビデンス集のどのファイルに収めたかを示す。網掛けは本ファイルに収めたものである。注2）個票（利用者票・職員個票）は収録していない。集計値のみである。担当者名・電話番号・メールアドレス及び施設の管理者名も収録していない。注3）見える化システムのδ（介護サービス自給率）には「本指標は自治体向けのため取り扱いに注意」との記載があるため、本集には収録していない。分析結果は成果品「地域差の分析」による。</t>
         </is>
@@ -949,7 +1045,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
